--- a/data/gravel/Giant Revolt X pro 1 short 2023.xlsx
+++ b/data/gravel/Giant Revolt X pro 1 short 2023.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel copy/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95CEB176-0D18-D04F-8852-642B68EF0C45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7AA9724-2E7E-FE43-B175-7C0FEA7CCD47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3140" yWindow="2340" windowWidth="24940" windowHeight="15000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="105">
   <si>
     <t>brand</t>
   </si>
@@ -317,6 +317,24 @@
   </si>
   <si>
     <t>frame size</t>
+  </si>
+  <si>
+    <t>class</t>
+  </si>
+  <si>
+    <t>gravel</t>
+  </si>
+  <si>
+    <t>handlebar</t>
+  </si>
+  <si>
+    <t>drop bar</t>
+  </si>
+  <si>
+    <t>fork</t>
+  </si>
+  <si>
+    <t>rigid</t>
   </si>
 </sst>
 </file>
@@ -655,7 +673,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H68"/>
+  <dimension ref="A1:H71"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1319,203 +1337,227 @@
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>57</v>
+        <v>99</v>
       </c>
       <c r="B34" t="s">
-        <v>58</v>
+        <v>100</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>59</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>93</v>
+        <v>101</v>
+      </c>
+      <c r="B35" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>60</v>
+        <v>103</v>
+      </c>
+      <c r="B36" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>61</v>
-      </c>
-      <c r="B37">
-        <v>53</v>
+        <v>57</v>
+      </c>
+      <c r="B37" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>62</v>
+        <v>59</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>63</v>
-      </c>
-      <c r="B39">
-        <v>40</v>
+        <v>60</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>64</v>
+        <v>61</v>
+      </c>
+      <c r="B40">
+        <v>53</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>66</v>
+        <v>63</v>
+      </c>
+      <c r="B42">
+        <v>40</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>69</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>94</v>
+        <v>66</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>71</v>
-      </c>
-      <c r="B47">
-        <v>30.9</v>
+        <v>68</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>74</v>
+        <v>71</v>
+      </c>
+      <c r="B50">
+        <v>30.9</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>75</v>
+        <v>72</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>78</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>95</v>
+        <v>75</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>79</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>95</v>
+        <v>76</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>81</v>
+        <v>78</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>82</v>
+        <v>79</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
         <v>92</v>
       </c>
     </row>
